--- a/data/reports/PHASE_3_STATISTICS.xlsx
+++ b/data/reports/PHASE_3_STATISTICS.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>557</v>
+        <v>559</v>
       </c>
     </row>
     <row r="5">
@@ -490,7 +490,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="8">
@@ -500,7 +500,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="9">
@@ -520,7 +520,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="11">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="4">
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="20">
@@ -846,7 +846,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="21">
@@ -936,7 +936,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="27">
@@ -981,7 +981,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="30">
@@ -1143,7 +1143,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>067</t>
+          <t>078</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -1153,7 +1153,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>078</t>
+          <t>067</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1183,17 +1183,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>049</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>056</t>
+          <t>348</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1213,7 +1213,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>049</t>
+          <t>056</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -2003,7 +2003,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>557</t>
+          <t>013</t>
         </is>
       </c>
       <c r="B98" t="n">
@@ -2013,7 +2013,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>013</t>
+          <t>029</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -2083,7 +2083,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>099</t>
+          <t>047</t>
         </is>
       </c>
       <c r="B106" t="n">
@@ -2113,7 +2113,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>029</t>
+          <t>099</t>
         </is>
       </c>
       <c r="B109" t="n">
@@ -2163,7 +2163,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>789</t>
+          <t>557</t>
         </is>
       </c>
       <c r="B114" t="n">
@@ -2183,11 +2183,11 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>589</t>
+          <t>789</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="117">
@@ -2243,7 +2243,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>045</t>
+          <t>126</t>
         </is>
       </c>
       <c r="B122" t="n">
@@ -2253,7 +2253,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>047</t>
+          <t>045</t>
         </is>
       </c>
       <c r="B123" t="n">
@@ -2283,7 +2283,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>128</t>
         </is>
       </c>
       <c r="B126" t="n">
@@ -2303,7 +2303,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>119</t>
         </is>
       </c>
       <c r="B128" t="n">
@@ -2323,7 +2323,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>589</t>
         </is>
       </c>
       <c r="B130" t="n">
@@ -3273,7 +3273,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>877</v>
+        <v>878</v>
       </c>
     </row>
     <row r="3">
@@ -3283,7 +3283,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>877</v>
+        <v>878</v>
       </c>
     </row>
   </sheetData>
@@ -3339,7 +3339,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>557</v>
+        <v>559</v>
       </c>
     </row>
     <row r="5">
@@ -3395,7 +3395,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="3">
@@ -3405,7 +3405,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="4">
@@ -3425,7 +3425,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="6">
